--- a/Scraping scripts/kanker_nl_master_table.xlsx
+++ b/Scraping scripts/kanker_nl_master_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="452">
   <si>
     <t>Cancer Type</t>
   </si>
@@ -592,7 +592,7 @@
     <t>Mesothelioom is kanker die in een vlies ontstaat, meestal in het longvlies. De belangrijkste oorzaak van mesothelioom is contact met asbest. Daarom heet de kanker ook wel asbestkanker. De vooruitzichten van mesothelioom zijn niet goed.</t>
   </si>
   <si>
-    <t>Bij mondkanker zit er een kwaadaardige tumor in de mond. Een tumor in demondkan op verschillende plekken zitten: onderin in je mond, in het gehemelte, in het tandvlees of aan de binnenkant van de wangen. De medische naam voor mondkanker is mondcarcinoom. Het is een vorm van hoofd-halskanker.</t>
+    <t>Mondkanker is kanker die in de mondholte ontstaat. Bijvoorbeeld onder je tong, in je wang of op je tandvlees. Het medische woord voor mondkanker is mondholtekanker of mondholtecarcinoom.</t>
   </si>
   <si>
     <t>MPN staat voor Myelo Proliferatieve Neoplasmata. Dit is een verzamelnaam voor 3 ziektes aan het beenmerg: polycythemia vera, essentiële trombocytemie en myelofibrose. Bij deze ziektes maakt je lichaam te veel of juist te weinig bloedcellen aan. MPN komen niet vaak voor: elk jaar krijgen ongeveer 1000 mensen deze diagnose.</t>
@@ -796,6 +796,9 @@
     <t>De vooruitzichten bij mesothelioom zijn niet goed. Je kunt niet genezen van mesothelioom. Gemiddeld leven mensen na de diagnose nog 13 tot 15 maanden. Je krijgt een behandeling om de ziekte te remmen en je klachten tegen te gaan. Lees verder over niet meer beter worden van kanker .</t>
   </si>
   <si>
+    <t>Begrijpelijk dat je meer wilt weten over je vooruitzichten. Is mondkanker goed te behandelen en wat kun je verwachten? Soms is daar iets over te zeggen, maar soms ook niet. De prognose van mondkanker hangt af van verschillende dingen. Bijvoorbeeld hoe vroeg de ziekte is ontdekt en waar de kanker precies zit. Wil je weten waar je aan toe bent? Vraag het je arts. Die kan misschien meer vertellen. Bekijk de overlevingscijfers van mondkanker .</t>
+  </si>
+  <si>
     <t>MPN zijn chronische ziektes. Je kunt er niet van genezen. De behandeling die je krijgt is om zo weinig mogelijk last te hebben van de ziekte. Wil je meer weten? Vraag het je arts. Die kan je meer vertellen.</t>
   </si>
   <si>
@@ -946,7 +949,7 @@
     <t>Een melanoom en de behandeling kunnen invloed hebben op je leven. Sommige mensen blijven last houden van de gevolgen van de behandeling. Bijvoorbeeld van het litteken na de operatie, lymfoedeem of vermoeidheid. Lees verder over klachten na een melanoom .</t>
   </si>
   <si>
-    <t>Mondkanker kan verschillende klachten geven. Zoals een zwelling of een zweer in de mond die soms pijn doet. Of rode of witte vlekken in de mond. Bij deze symptomen denken artsen niet altijd direct aan mondkanker. Lees verder over de symptomen bij mondkanker .</t>
+    <t>Mondkanker kun je merken aan een zweertje of een zwelling in je mond. Of je hebt rode of witte verdikte plekken in je mond. Lees verder over de symptomen bij mondkanker.</t>
   </si>
   <si>
     <t>Er zijn veel verschillende klachten bij MPN. Zoals vermoeidheid, hoofdpijn of jeuk. Of nachtzweten, afvallen of pijn in je botten. Maar deze klachten komen heel vaak voor. Meestal hebben ze een andere oorzaak. Vaak worden MPN toevallig ontdekt, bijvoorbeeld bij een bloedonderzoek. MPN zijn lastig te herkennen.</t>
@@ -1105,7 +1108,7 @@
     <t>Er zijn factoren die het risico op een melanoom groter maken. Zoals verbranding door de zon als je jong bent, een lichte huid of een erfelijke aanleg. Lees verder over de oorzaken en risicofactoren bij een melanoom .</t>
   </si>
   <si>
-    <t>De belangrijkste oorzaken van mondkanker zijn roken en veel alcohol drinken. Er zijn ook nog een paar andere risicofactoren. Bekijk de risicofactoren van mondkanker .</t>
+    <t>Er zijn factoren die het risico op mondkanker groter maken, zoals roken en alcohol drinken. Lees verder over de oorzaken en risicofactoren bij mondkanker .</t>
   </si>
   <si>
     <t>Bij MPN gaat er iets mis bij het maken van bloedcellen in het beenmerg. Er worden dan te veel of te weinig bloedcellen gemaakt. De oorzaak hiervan is een fout in het DNA (een mutatie) in de stamcellen. Stamcellen zijn cellen in het beenmerg die bloedcellen worden. Lees verder over beenmerg en bloedcellen en MPN .</t>
@@ -1282,7 +1285,7 @@
     <t>Van mesothelioom kun je niet genezen. Je krijgt een behandeling om je leven te verlengen of je klachten te verminderen. Mogelijke behandelingen zijn immunotherapie, chemotherapie of bestraling. Soms krijg je een combinatie van behandelingen. Lees verder over de behandelingen van mesothelioom .</t>
   </si>
   <si>
-    <t>Bij mondkanker zijn verschillende behandelingen mogelijk. Bij kans op genezing is de operatie de meest gebruikte behandeling. Na de operatie volgt meestal een nabehandeling met bestraling, of met chemoradiatie. Als genezing niet meer mogelijk is, zijn er verschillende behandelingen die de ziekte kunnen remmen. Zoals bestraling, chemotherapie en immunotherapie. Bekijk de uitgebreide informatie over de behandeling van mondkanker .</t>
+    <t>Er zijn verschillende behandelingen bij mondkanker. De meeste mensen krijgen een operatie. Maar bestraling kan ook, als eerste behandeling of na een andere behandeling. Soms krijg je een combinatie van behandelingen, bijvoorbeeld bestraling en chemotherapie (chemoradiatie). Lees verder over behandelingen bij mondkanker.</t>
   </si>
   <si>
     <t>Welke behandeling je krijgt, ligt onder andere aan de soort MPN die je hebt. Door MPN kunnen bloedstolsels ontstaan. Daarom heb je een groter risico op een embolie of trombose. Veel mensen krijgen bloedverdunners om dit te voorkomen. Je kunt ook medicijnen krijgen die de extra aanmaak van de bloedcellen stoppen. Lees verder over de behandeling van MPN .</t>
@@ -1777,13 +1780,13 @@
         <v>226</v>
       </c>
       <c r="E2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1800,13 +1803,13 @@
         <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1826,10 +1829,10 @@
         <v>238</v>
       </c>
       <c r="F4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1846,13 +1849,13 @@
         <v>229</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F5" t="s">
         <v>238</v>
       </c>
       <c r="G5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1869,13 +1872,13 @@
         <v>230</v>
       </c>
       <c r="E6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1892,13 +1895,13 @@
         <v>231</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1918,10 +1921,10 @@
         <v>238</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1938,13 +1941,13 @@
         <v>233</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F9" t="s">
         <v>238</v>
       </c>
       <c r="G9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1961,13 +1964,13 @@
         <v>234</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1984,13 +1987,13 @@
         <v>235</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2007,13 +2010,13 @@
         <v>236</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2030,13 +2033,13 @@
         <v>237</v>
       </c>
       <c r="E13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2076,13 +2079,13 @@
         <v>239</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2122,13 +2125,13 @@
         <v>240</v>
       </c>
       <c r="E17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2145,13 +2148,13 @@
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F18" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2168,13 +2171,13 @@
         <v>242</v>
       </c>
       <c r="E19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G19" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2191,13 +2194,13 @@
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F20" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2214,13 +2217,13 @@
         <v>244</v>
       </c>
       <c r="E21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G21" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2237,13 +2240,13 @@
         <v>245</v>
       </c>
       <c r="E22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F22" t="s">
         <v>238</v>
       </c>
       <c r="G22" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2260,13 +2263,13 @@
         <v>246</v>
       </c>
       <c r="E23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F23" t="s">
         <v>238</v>
       </c>
       <c r="G23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2283,13 +2286,13 @@
         <v>247</v>
       </c>
       <c r="E24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F24" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2306,13 +2309,13 @@
         <v>248</v>
       </c>
       <c r="E25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F25" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G25" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2358,7 +2361,7 @@
         <v>238</v>
       </c>
       <c r="G27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2378,10 +2381,10 @@
         <v>238</v>
       </c>
       <c r="F28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G28" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2421,13 +2424,13 @@
         <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G30" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2444,13 +2447,13 @@
         <v>252</v>
       </c>
       <c r="E31" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G31" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2467,13 +2470,13 @@
         <v>253</v>
       </c>
       <c r="E32" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F32" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G32" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2490,13 +2493,13 @@
         <v>238</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G33" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2519,7 +2522,7 @@
         <v>238</v>
       </c>
       <c r="G34" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2536,13 +2539,13 @@
         <v>255</v>
       </c>
       <c r="E35" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G35" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2582,13 +2585,13 @@
         <v>256</v>
       </c>
       <c r="E37" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F37" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G37" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2605,13 +2608,13 @@
         <v>257</v>
       </c>
       <c r="E38" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F38" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G38" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2634,7 +2637,7 @@
         <v>238</v>
       </c>
       <c r="G39" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2657,7 +2660,7 @@
         <v>238</v>
       </c>
       <c r="G40" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2671,16 +2674,16 @@
         <v>192</v>
       </c>
       <c r="D41" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="E41" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F41" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2694,16 +2697,16 @@
         <v>193</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E42" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F42" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G42" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2717,16 +2720,16 @@
         <v>194</v>
       </c>
       <c r="D43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F43" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G43" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2740,16 +2743,16 @@
         <v>195</v>
       </c>
       <c r="D44" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E44" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F44" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G44" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2809,16 +2812,16 @@
         <v>198</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E47" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F47" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G47" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2832,16 +2835,16 @@
         <v>199</v>
       </c>
       <c r="D48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E48" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F48" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2855,16 +2858,16 @@
         <v>200</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E49" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F49" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G49" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2878,16 +2881,16 @@
         <v>201</v>
       </c>
       <c r="D50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E50" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F50" t="s">
         <v>238</v>
       </c>
       <c r="G50" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2901,16 +2904,16 @@
         <v>202</v>
       </c>
       <c r="D51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E51" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F51" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G51" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2927,13 +2930,13 @@
         <v>238</v>
       </c>
       <c r="E52" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F52" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G52" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2947,16 +2950,16 @@
         <v>204</v>
       </c>
       <c r="D53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E53" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G53" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2970,16 +2973,16 @@
         <v>205</v>
       </c>
       <c r="D54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E54" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G54" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2993,16 +2996,16 @@
         <v>206</v>
       </c>
       <c r="D55" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E55" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F55" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G55" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3016,16 +3019,16 @@
         <v>207</v>
       </c>
       <c r="D56" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
         <v>238</v>
       </c>
       <c r="F56" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G56" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3039,16 +3042,16 @@
         <v>208</v>
       </c>
       <c r="D57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E57" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F57" t="s">
         <v>238</v>
       </c>
       <c r="G57" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3062,16 +3065,16 @@
         <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E58" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F58" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G58" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3085,16 +3088,16 @@
         <v>210</v>
       </c>
       <c r="D59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E59" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F59" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G59" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3108,16 +3111,16 @@
         <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E60" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F60" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G60" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3134,13 +3137,13 @@
         <v>238</v>
       </c>
       <c r="E61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F61" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G61" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3154,16 +3157,16 @@
         <v>213</v>
       </c>
       <c r="D62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E62" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F62" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G62" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3177,16 +3180,16 @@
         <v>214</v>
       </c>
       <c r="D63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E63" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F63" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G63" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3223,16 +3226,16 @@
         <v>216</v>
       </c>
       <c r="D65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E65" t="s">
         <v>238</v>
       </c>
       <c r="F65" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G65" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3249,13 +3252,13 @@
         <v>238</v>
       </c>
       <c r="E66" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F66" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G66" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3272,13 +3275,13 @@
         <v>238</v>
       </c>
       <c r="E67" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F67" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G67" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3315,16 +3318,16 @@
         <v>220</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F69" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G69" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3338,16 +3341,16 @@
         <v>221</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F70" t="s">
         <v>238</v>
       </c>
       <c r="G70" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3364,13 +3367,13 @@
         <v>238</v>
       </c>
       <c r="E71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F71" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G71" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3384,16 +3387,16 @@
         <v>223</v>
       </c>
       <c r="D72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G72" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3430,16 +3433,16 @@
         <v>225</v>
       </c>
       <c r="D74" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F74" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G74" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
